--- a/processed_ruby_restored_xlsx/sc221_瑠璃３：なぐさめちゅー.ss.xlsx
+++ b/processed_ruby_restored_xlsx/sc221_瑠璃３：なぐさめちゅー.ss.xlsx
@@ -574,9 +574,9 @@
       </c>
       <c r="B8" s="1" t="inlineStr">
         <is>
-          <t>On the afternoon of the second day of summer vacation,
-Rurichiyo-chan and I were preparing the ingredients
-for a meal together.</t>
+          <t>On the afternoon of the second day of summer
+vacation, Rurichiyo-chan and I were preparing the
+ingredients for a meal together.</t>
         </is>
       </c>
       <c r="C8" t="n">
@@ -591,8 +591,9 @@
       </c>
       <c r="B9" s="1" t="inlineStr">
         <is>
-          <t>With everyone else having gone back to their families,
-it was just the two of them in the spacious dorm...</t>
+          <t>With everyone else having gone back to their
+families, it was just the two of them in the spacious
+dorm...</t>
         </is>
       </c>
       <c r="C9" t="n">
@@ -1392,8 +1393,9 @@
       </c>
       <c r="B61" s="1" t="inlineStr">
         <is>
-          <t>Kikuchiyo-baa-chan was all goo-goo over Rurichiyo-chan
-again today and didn't even look at me.</t>
+          <t>Kikuchiyo-baa-chan was all goo-goo over
+Rurichiyo-chan again today and didn't even look at
+me.</t>
         </is>
       </c>
       <c r="C61" t="n">
@@ -1667,8 +1669,9 @@
       </c>
       <c r="B79" s="1" t="inlineStr">
         <is>
-          <t>「Rurichiyo. I missed you yesterday—didn’t I~？ I stayed
-at home and behaved like a good kid waiting for you.」</t>
+          <t>「Rurichiyo. I missed you yesterday—didn’t I~？ I
+stayed at home and behaved like a good kid waiting
+for you.」</t>
         </is>
       </c>
       <c r="C79" t="n">
@@ -1759,8 +1762,8 @@
       </c>
       <c r="B85" s="1" t="inlineStr">
         <is>
-          <t>「Nope？ Rurichiyo, do as you like. Once you leave home,
-it’s your freedom.」</t>
+          <t>「Nope？ Rurichiyo, do as you like. Once you leave
+home, it’s your freedom.」</t>
         </is>
       </c>
       <c r="C85" t="n">
@@ -1867,9 +1870,9 @@
       </c>
       <c r="B92" s="1" t="inlineStr">
         <is>
-          <t>...Kikuchiyo-baa-chan seemed to be having a great time
-talking with Rurichiyo-chan, and she kept chattering
-about trivial things.</t>
+          <t>...Kikuchiyo-baa-chan seemed to be having a great
+time talking with Rurichiyo-chan, and she kept
+chattering about trivial things.</t>
         </is>
       </c>
       <c r="C92" t="n">
@@ -1884,9 +1887,9 @@
       </c>
       <c r="B93" s="1" t="inlineStr">
         <is>
-          <t>They were really talking about utterly inconsequential
-stuff, and I kept on with the prep while listening
-from the side.</t>
+          <t>They were really talking about utterly
+inconsequential stuff, and I kept on with the prep
+while listening from the side.</t>
         </is>
       </c>
       <c r="C93" t="n">
@@ -2053,8 +2056,8 @@
       </c>
       <c r="B104" s="1" t="inlineStr">
         <is>
-          <t>It seems like it'll end on a peaceful note, but that's
-not how things are going to go — as usual.</t>
+          <t>It seems like it'll end on a peaceful note, but
+that's not how things are going to go — as usual.</t>
         </is>
       </c>
       <c r="C104" t="n">
@@ -2373,7 +2376,8 @@
       </c>
       <c r="B125" s="1" t="inlineStr">
         <is>
-          <t>…It’s like a cursed ichimatsu doll and it’s not funny.</t>
+          <t>…It’s like a cursed ichimatsu doll and it’s not
+funny.</t>
         </is>
       </c>
       <c r="C125" t="n">
@@ -2494,9 +2498,9 @@
       </c>
       <c r="B133" s="1" t="inlineStr">
         <is>
-          <t>I thought she pushed Rurichiyo away because she wanted
-to have a conversation she couldn't have in front of
-Rurichiyo...</t>
+          <t>I thought she pushed Rurichiyo away because she
+wanted to have a conversation she couldn't have in
+front of Rurichiyo...</t>
         </is>
       </c>
       <c r="C133" t="n">
@@ -3067,8 +3071,9 @@
       <c r="B170" s="1" t="inlineStr">
         <is>
           <t>「What you're doing is, to put it bluntly, just being
-spoiled. Even if you work at Arisugawa, as a member of
-society you need to straighten out your thinking…！」</t>
+spoiled. Even if you work at Arisugawa, as a member
+of society you need to straighten out your
+thinking…！」</t>
         </is>
       </c>
       <c r="C170" t="n">
@@ -3205,9 +3210,9 @@
       </c>
       <c r="B179" s="1" t="inlineStr">
         <is>
-          <t>She probably didn't go to see Rurichiyo before leaving
-because if she saw her face she'd start talking again
-and wouldn't be able to leave.</t>
+          <t>She probably didn't go to see Rurichiyo before
+leaving because if she saw her face she'd start
+talking again and wouldn't be able to leave.</t>
         </is>
       </c>
       <c r="C179" t="n">
@@ -3732,8 +3737,8 @@
       </c>
       <c r="B213" s="1" t="inlineStr">
         <is>
-          <t>「...But when I'm told to cut it head-on, she just ends
-up feeling pathetic.」</t>
+          <t>「...But when I'm told to cut it head-on, she just
+ends up feeling pathetic.」</t>
         </is>
       </c>
       <c r="C213" t="n">
@@ -4373,8 +4378,8 @@
       </c>
       <c r="B255" s="1" t="inlineStr">
         <is>
-          <t>「Well, I guess she means she'd like me to take care of
-her daily life, right？」</t>
+          <t>「Well, I guess she means she'd like me to take care
+of her daily life, right？」</t>
         </is>
       </c>
       <c r="C255" t="n">
@@ -5477,7 +5482,8 @@
       </c>
       <c r="B327" s="1" t="inlineStr">
         <is>
-          <t>「Then… more… chu, chupr, puchu… chu！ lero lero lero…！」</t>
+          <t>「Then… more… chu, chupr, puchu… chu！ lero lero
+lero…！」</t>
         </is>
       </c>
       <c r="C327" t="n">
@@ -5538,8 +5544,8 @@
       </c>
       <c r="B331" s="1" t="inlineStr">
         <is>
-          <t>I can just barely see Rurichiyo-chan's tongue sticking
-out.</t>
+          <t>I can just barely see Rurichiyo-chan's tongue
+sticking out.</t>
         </is>
       </c>
       <c r="C331" t="n">
@@ -5569,8 +5575,8 @@
       </c>
       <c r="B333" s="1" t="inlineStr">
         <is>
-          <t>「churu, nn！ amu... rero, rerorero... fuu... afu, rero,
-pfu... nn！」</t>
+          <t>「churu, nn！ amu... rero, rerorero... fuu... afu,
+rero, pfu... nn！」</t>
         </is>
       </c>
       <c r="C333" t="n">
@@ -5585,8 +5591,8 @@
       </c>
       <c r="B334" s="1" t="inlineStr">
         <is>
-          <t>I stick my tongue all the way out and watch from above
-as Rurichiyo-chan licks it for me.</t>
+          <t>I stick my tongue all the way out and watch from
+above as Rurichiyo-chan licks it for me.</t>
         </is>
       </c>
       <c r="C334" t="n">
@@ -5632,8 +5638,8 @@
       </c>
       <c r="B337" s="1" t="inlineStr">
         <is>
-          <t>…The sensation of a kiss is felt with the tongue; it's
-not really something you can see.</t>
+          <t>…The sensation of a kiss is felt with the tongue;
+it's not really something you can see.</t>
         </is>
       </c>
       <c r="C337" t="n">
@@ -6282,9 +6288,9 @@
       </c>
       <c r="B379" s="1" t="inlineStr">
         <is>
-          <t>And besides, because Rurichiyo-chan has always been so
-sweet to me, I can’t help but want to snuggle up and
-be spoiled.</t>
+          <t>And besides, because Rurichiyo-chan has always been
+so sweet to me, I can’t help but want to snuggle up
+and be spoiled.</t>
         </is>
       </c>
       <c r="C379" t="n">
@@ -6606,9 +6612,9 @@
       </c>
       <c r="B400" s="1" t="inlineStr">
         <is>
-          <t>…Thinking about being jerked off while acting all cute
-and clingy to a little kid makes my body arch back
-without me even meaning to.</t>
+          <t>…Thinking about being jerked off while acting all
+cute and clingy to a little kid makes my body arch
+back without me even meaning to.</t>
         </is>
       </c>
       <c r="C400" t="n">
@@ -7563,8 +7569,8 @@
       <c r="B462" s="1" t="inlineStr">
         <is>
           <t>...Relaxing into that safety, I didn't notice it
-rising until the sensation of coming swelled up inside
-me.</t>
+rising until the sensation of coming swelled up
+inside me.</t>
         </is>
       </c>
       <c r="C462" t="n">
@@ -7655,8 +7661,8 @@
       </c>
       <c r="B468" s="1" t="inlineStr">
         <is>
-          <t>At the unexpected tempo-up, my penis wanted to hit the
-brakes.</t>
+          <t>At the unexpected tempo-up, my penis wanted to hit
+the brakes.</t>
         </is>
       </c>
       <c r="C468" t="n">
@@ -7960,8 +7966,8 @@
       </c>
       <c r="B488" s="1" t="inlineStr">
         <is>
-          <t>At last the ejaculation began, and I was swept away by
-that sensation and the bliss of the kiss.</t>
+          <t>At last the ejaculation began, and I was swept away
+by that sensation and the bliss of the kiss.</t>
         </is>
       </c>
       <c r="C488" t="n">
@@ -7991,8 +7997,8 @@
       </c>
       <c r="B490" s="1" t="inlineStr">
         <is>
-          <t>「Ah...！？ Nn, n'uu... chuku, chu, chu！ Nfuuuh... chupu,
-puchu...！」</t>
+          <t>「Ah...！？ Nn, n'uu... chuku, chu, chu！ Nfuuuh...
+chupu, puchu...！」</t>
         </is>
       </c>
       <c r="C490" t="n">
@@ -8113,8 +8119,8 @@
       </c>
       <c r="B498" s="1" t="inlineStr">
         <is>
-          <t>I went slack with no control left, and she noticed and
-laughed at me.</t>
+          <t>I went slack with no control left, and she noticed
+and laughed at me.</t>
         </is>
       </c>
       <c r="C498" t="n">
@@ -8267,8 +8273,8 @@
       </c>
       <c r="B508" s="1" t="inlineStr">
         <is>
-          <t>The penis that was praised for ejaculating also lowers
-its head, looking bashful.</t>
+          <t>The penis that was praised for ejaculating also
+lowers its head, looking bashful.</t>
         </is>
       </c>
       <c r="C508" t="n">
@@ -8495,8 +8501,8 @@
       </c>
       <c r="B523" s="1" t="inlineStr">
         <is>
-          <t>She smiles sweetly, laughing gracefully, and is gently
-stroking my penis...</t>
+          <t>She smiles sweetly, laughing gracefully, and is
+gently stroking my penis...</t>
         </is>
       </c>
       <c r="C523" t="n">

--- a/processed_ruby_restored_xlsx/sc221_瑠璃３：なぐさめちゅー.ss.xlsx
+++ b/processed_ruby_restored_xlsx/sc221_瑠璃３：なぐさめちゅー.ss.xlsx
@@ -2422,7 +2422,7 @@
       </c>
       <c r="B128" s="1" t="inlineStr">
         <is>
-          <t>I cut me off and spoke.</t>
+          <t>I cut him off and spoke.</t>
         </is>
       </c>
       <c r="C128" t="n">
@@ -3627,8 +3627,8 @@
       </c>
       <c r="B206" s="1" t="inlineStr">
         <is>
-          <t>「W-well... someone like Grandma thinks so deeply that
-someone like me couldn't possibly compare...」</t>
+          <t>W-well... someone like Grandma thinks so deeply that
+someone like me couldn't possibly compare...</t>
         </is>
       </c>
       <c r="C206" t="n">
@@ -3997,7 +3997,7 @@
       </c>
       <c r="B230" s="1" t="inlineStr">
         <is>
-          <t>Rurichiyo</t>
+          <t>Ruri</t>
         </is>
       </c>
       <c r="C230" t="n">
@@ -4088,7 +4088,7 @@
       </c>
       <c r="B236" s="1" t="inlineStr">
         <is>
-          <t>Rurichiyo</t>
+          <t>Ruri</t>
         </is>
       </c>
       <c r="C236" t="n">
@@ -4611,7 +4611,7 @@
       </c>
       <c r="B270" s="1" t="inlineStr">
         <is>
-          <t>「Nn…」</t>
+          <t>Nn…</t>
         </is>
       </c>
       <c r="C270" t="n">
@@ -4870,7 +4870,7 @@
       </c>
       <c r="B287" s="1" t="inlineStr">
         <is>
-          <t>「Oh... cheer up now, okay... mwah！」</t>
+          <t>Oh... cheer up now, okay... mwah！</t>
         </is>
       </c>
       <c r="C287" t="n">
@@ -4946,7 +4946,7 @@
       </c>
       <c r="B292" s="1" t="inlineStr">
         <is>
-          <t>「Mmph... smoo, smoo...！」</t>
+          <t>Mmph... smoo, smoo...！</t>
         </is>
       </c>
       <c r="C292" t="n">
@@ -5452,7 +5452,7 @@
       </c>
       <c r="B325" s="1" t="inlineStr">
         <is>
-          <t>「Ah... ahh... yeah, I guess so...」</t>
+          <t>Ah... ahh... yeah, I guess so...</t>
         </is>
       </c>
       <c r="C325" t="n">
@@ -6211,7 +6211,7 @@
       </c>
       <c r="B374" s="1" t="inlineStr">
         <is>
-          <t>Rurichiyo</t>
+          <t>Ruri</t>
         </is>
       </c>
       <c r="C374" t="n">
@@ -6305,7 +6305,7 @@
       </c>
       <c r="B380" s="1" t="inlineStr">
         <is>
-          <t>Rurichiyo</t>
+          <t>Rurichiyo-chan</t>
         </is>
       </c>
       <c r="C380" t="n">
@@ -6382,7 +6382,7 @@
       </c>
       <c r="B385" s="1" t="inlineStr">
         <is>
-          <t>Rurichiyo</t>
+          <t>Rurichiyo-chan</t>
         </is>
       </c>
       <c r="C385" t="n">
@@ -6459,7 +6459,7 @@
       </c>
       <c r="B390" s="1" t="inlineStr">
         <is>
-          <t>Rurichiyo</t>
+          <t>Rurichiyo-chan</t>
         </is>
       </c>
       <c r="C390" t="n">
@@ -6551,7 +6551,7 @@
       </c>
       <c r="B396" s="1" t="inlineStr">
         <is>
-          <t>Rurichiyo</t>
+          <t>Rurichiyo-chan</t>
         </is>
       </c>
       <c r="C396" t="n">
@@ -6843,7 +6843,7 @@
       </c>
       <c r="B415" s="1" t="inlineStr">
         <is>
-          <t>While kissing and smooching, she gently strokes my
+          <t>While kissing and smooching, she gently strokes his
 penis.</t>
         </is>
       </c>
@@ -7289,7 +7289,7 @@
       </c>
       <c r="B444" s="1" t="inlineStr">
         <is>
-          <t>「Goodness, I'm so cute, what should I do…！」</t>
+          <t>「Goodness, he's so cute, what should I do…！」</t>
         </is>
       </c>
       <c r="C444" t="n">
@@ -8089,7 +8089,7 @@
       </c>
       <c r="B496" s="1" t="inlineStr">
         <is>
-          <t>Rurichiyo</t>
+          <t>Ruri</t>
         </is>
       </c>
       <c r="C496" t="n">
@@ -8502,7 +8502,7 @@
       <c r="B523" s="1" t="inlineStr">
         <is>
           <t>She smiles sweetly, laughing gracefully, and is
-gently stroking my penis...</t>
+gently stroking his penis...</t>
         </is>
       </c>
       <c r="C523" t="n">
